--- a/artfynd/A 40778-2026 artfynd.xlsx
+++ b/artfynd/A 40778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373101</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373105</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373100</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>137373058</v>
       </c>
       <c r="B29" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137373080</v>
       </c>
       <c r="B30" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>137373095</v>
       </c>
       <c r="B31" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137373103</v>
       </c>
       <c r="B32" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>137373084</v>
       </c>
       <c r="B33" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 40778-2026 artfynd.xlsx
+++ b/artfynd/A 40778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373101</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373105</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373100</v>
       </c>
       <c r="B4" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>137373058</v>
       </c>
       <c r="B29" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137373080</v>
       </c>
       <c r="B30" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>137373095</v>
       </c>
       <c r="B31" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137373103</v>
       </c>
       <c r="B32" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>137373084</v>
       </c>
       <c r="B33" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 40778-2026 artfynd.xlsx
+++ b/artfynd/A 40778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373101</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373105</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373100</v>
       </c>
       <c r="B4" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>137373058</v>
       </c>
       <c r="B29" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137373080</v>
       </c>
       <c r="B30" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>137373095</v>
       </c>
       <c r="B31" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137373103</v>
       </c>
       <c r="B32" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>137373084</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 40778-2026 artfynd.xlsx
+++ b/artfynd/A 40778-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373101</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373105</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373100</v>
       </c>
       <c r="B4" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373068</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137373070</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>137373081</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>137373086</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137373090</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137373092</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>137373094</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>137373099</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>137373106</v>
       </c>
       <c r="B13" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137373108</v>
       </c>
       <c r="B14" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137393054</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>137373065</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137373076</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137373060</v>
       </c>
       <c r="B18" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>137373058</v>
       </c>
       <c r="B29" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>137373080</v>
       </c>
       <c r="B30" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>137373095</v>
       </c>
       <c r="B31" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>137373103</v>
       </c>
       <c r="B32" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>137373084</v>
       </c>
       <c r="B33" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
